--- a/research/traditional_assets/database/data/nigeria/nigeria_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03325</v>
+        <v>0.1833</v>
       </c>
       <c r="E2">
-        <v>0.10316</v>
+        <v>0.28135</v>
       </c>
       <c r="G2">
-        <v>0.002371000288267513</v>
+        <v>0.003490098532616031</v>
       </c>
       <c r="H2">
-        <v>0.002371000288267513</v>
+        <v>0.003490098532616031</v>
       </c>
       <c r="I2">
-        <v>-0.0006149706928029212</v>
+        <v>0.00196679585815931</v>
       </c>
       <c r="J2">
-        <v>-0.0005890866151098872</v>
+        <v>0.001483997411795781</v>
       </c>
       <c r="K2">
-        <v>130.96</v>
+        <v>164.51</v>
       </c>
       <c r="L2">
-        <v>0.3145959450369944</v>
+        <v>0.317213320221361</v>
       </c>
       <c r="M2">
-        <v>127.4</v>
+        <v>106.31</v>
       </c>
       <c r="N2">
-        <v>0.1016111022491626</v>
+        <v>0.09707789242991509</v>
       </c>
       <c r="O2">
-        <v>0.9728161270616982</v>
+        <v>0.646222114157194</v>
       </c>
       <c r="P2">
-        <v>127.4</v>
+        <v>106.31</v>
       </c>
       <c r="Q2">
-        <v>0.1016111022491626</v>
+        <v>0.09707789242991509</v>
       </c>
       <c r="R2">
-        <v>0.9728161270616982</v>
+        <v>0.646222114157194</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>708.79</v>
+        <v>420.09</v>
       </c>
       <c r="V2">
-        <v>0.5653134471207529</v>
+        <v>0.383608802849055</v>
       </c>
       <c r="W2">
-        <v>0.1648822031500239</v>
+        <v>0.1872454323286396</v>
       </c>
       <c r="X2">
-        <v>0.03877543482653724</v>
+        <v>0.07250316683028661</v>
       </c>
       <c r="Y2">
-        <v>0.1261067683234867</v>
+        <v>0.114742265498353</v>
       </c>
       <c r="Z2">
-        <v>0.5261607882047361</v>
+        <v>0.6949044893233857</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04247161640166496</v>
+        <v>0.07883561814867397</v>
       </c>
       <c r="AC2">
-        <v>-0.04460125655683964</v>
+        <v>-0.07883561814867397</v>
       </c>
       <c r="AD2">
-        <v>484.26</v>
+        <v>637.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>484.26</v>
+        <v>637.1</v>
       </c>
       <c r="AG2">
-        <v>-224.53</v>
+        <v>217.01</v>
       </c>
       <c r="AH2">
-        <v>0.278620991220096</v>
+        <v>0.3677981757302852</v>
       </c>
       <c r="AI2">
-        <v>0.3509969775381069</v>
+        <v>0.3948387736509726</v>
       </c>
       <c r="AJ2">
-        <v>-0.2181448988117792</v>
+        <v>0.1653900968668786</v>
       </c>
       <c r="AK2">
-        <v>-0.3346798235153827</v>
+        <v>0.1818296075342695</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AN2">
-        <v>490.6382978723404</v>
+        <v>328.4020618556701</v>
+      </c>
+      <c r="AO2">
+        <v>0.2608695652173913</v>
       </c>
       <c r="AP2">
-        <v>-227.4873353596758</v>
+        <v>111.860824742268</v>
+      </c>
+      <c r="AQ2">
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stanbic IBTC Holdings PLC (NGSE:STANBIC)</t>
+          <t>The Nigerian Exchange Group Plc (NGSE:NGXGROUP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,110 +721,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.107</v>
-      </c>
-      <c r="E3">
-        <v>0.202</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1071005917159763</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1071005917159763</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.06035502958579882</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.04830697234908993</v>
       </c>
       <c r="K3">
-        <v>133.1</v>
+        <v>2.11</v>
       </c>
       <c r="L3">
-        <v>0.329537014112404</v>
+        <v>0.1248520710059172</v>
       </c>
       <c r="M3">
-        <v>127.4</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1127234117855247</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.9571750563486101</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>127.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1127234117855247</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.9571750563486101</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>651.8</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.576712086356397</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1420036274405206</v>
+        <v>0.026375</v>
       </c>
       <c r="X3">
-        <v>0.03895058745021487</v>
+        <v>0.07165073593751631</v>
       </c>
       <c r="Y3">
-        <v>0.1030530399903058</v>
+        <v>-0.04527573593751631</v>
       </c>
       <c r="Z3">
-        <v>0.5112011137830655</v>
+        <v>0.256940432389698</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.01241201436281235</v>
       </c>
       <c r="AB3">
-        <v>0.04192155341888852</v>
+        <v>0.07693872039749275</v>
       </c>
       <c r="AC3">
-        <v>-0.04192155341888852</v>
+        <v>-0.0645267060346804</v>
       </c>
       <c r="AD3">
-        <v>466.5</v>
+        <v>33.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>466.5</v>
+        <v>33.7</v>
       </c>
       <c r="AG3">
-        <v>-185.3</v>
+        <v>33.7</v>
       </c>
       <c r="AH3">
-        <v>0.2921650904991545</v>
+        <v>0.2348432055749129</v>
       </c>
       <c r="AI3">
-        <v>0.346608217549595</v>
+        <v>0.2728744939271255</v>
       </c>
       <c r="AJ3">
-        <v>-0.1961054079796803</v>
+        <v>0.2348432055749129</v>
       </c>
       <c r="AK3">
-        <v>-0.2669644143495173</v>
+        <v>0.2728744939271255</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>3.91</v>
+      </c>
+      <c r="AN3">
+        <v>17.37113402061856</v>
+      </c>
+      <c r="AO3">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="AP3">
+        <v>17.37113402061856</v>
+      </c>
+      <c r="AQ3">
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="4">
@@ -837,6 +846,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.27</v>
+      </c>
+      <c r="E4">
+        <v>0.464</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -850,82 +865,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="L4">
-        <v>0.490909090909091</v>
+        <v>0.3480278422273782</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0452513966480447</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.54</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0452513966480447</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.54</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>4.99</v>
+        <v>3.29</v>
       </c>
       <c r="V4">
-        <v>0.3960317460317461</v>
+        <v>0.1837988826815643</v>
       </c>
       <c r="W4">
-        <v>0.1877607788595271</v>
+        <v>0.2252252252252252</v>
       </c>
       <c r="X4">
-        <v>0.0386002822028596</v>
+        <v>0.07250316683028661</v>
       </c>
       <c r="Y4">
-        <v>0.1491604966566675</v>
+        <v>0.1527220583949386</v>
       </c>
       <c r="Z4">
-        <v>0.44</v>
+        <v>0.6600306278713629</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0430216793844414</v>
+        <v>0.07883561814867397</v>
       </c>
       <c r="AC4">
-        <v>-0.0430216793844414</v>
+        <v>-0.07883561814867397</v>
       </c>
       <c r="AD4">
-        <v>4.86</v>
+        <v>6.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4.86</v>
+        <v>6.3</v>
       </c>
       <c r="AG4">
-        <v>-0.1299999999999999</v>
+        <v>3.01</v>
       </c>
       <c r="AH4">
-        <v>0.2783505154639175</v>
+        <v>0.2603305785123967</v>
       </c>
       <c r="AI4">
-        <v>0.4218750000000001</v>
+        <v>0.4820198928844682</v>
       </c>
       <c r="AJ4">
-        <v>-0.01042502004811547</v>
+        <v>0.1439502630320421</v>
       </c>
       <c r="AK4">
-        <v>-0.01990811638591116</v>
+        <v>0.3077709611451943</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -942,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abbey Mortgage Bank Plc (NGSE:ABBEYBDS)</t>
+          <t>Stanbic IBTC Holdings PLC (NGSE:STANBIC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -950,204 +968,109 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.0987</v>
+      </c>
       <c r="G5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>-8.31</v>
+        <v>160.9</v>
       </c>
       <c r="L5">
-        <v>1.859060402684564</v>
+        <v>0.3234821069561721</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>105.5</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1090551995038247</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.6556867619639527</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>105.5</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1090551995038247</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.6556867619639527</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>52</v>
+        <v>416.8</v>
       </c>
       <c r="V5">
-        <v>3.190184049079754</v>
+        <v>0.4308455654331197</v>
       </c>
       <c r="W5">
-        <v>-0.4350785340314136</v>
+        <v>0.1872454323286396</v>
       </c>
       <c r="X5">
-        <v>0.04385523637497868</v>
+        <v>0.0775243259134827</v>
       </c>
       <c r="Y5">
-        <v>-0.4789337704063923</v>
+        <v>0.1097211064151569</v>
       </c>
       <c r="Z5">
-        <v>0.862102217936355</v>
+        <v>0.7379821958456972</v>
       </c>
       <c r="AA5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04618083372923787</v>
+        <v>0.08489161065392201</v>
       </c>
       <c r="AC5">
-        <v>-0.04618083372923787</v>
+        <v>-0.08489161065392201</v>
       </c>
       <c r="AD5">
-        <v>12.9</v>
+        <v>597.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>12.9</v>
+        <v>597.1</v>
       </c>
       <c r="AG5">
-        <v>-39.1</v>
+        <v>180.3</v>
       </c>
       <c r="AH5">
-        <v>0.4417808219178082</v>
+        <v>0.38165548098434</v>
       </c>
       <c r="AI5">
-        <v>0.5797752808988764</v>
+        <v>0.4042654028436019</v>
       </c>
       <c r="AJ5">
-        <v>1.714912280701754</v>
+        <v>0.1570968023002527</v>
       </c>
       <c r="AK5">
-        <v>1.314285714285714</v>
+        <v>0.1700622524052066</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nigerian Exchange Group Plc (NGSE:NGXGROUP)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-0.0405</v>
-      </c>
-      <c r="E6">
-        <v>0.00432</v>
-      </c>
-      <c r="G6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I6">
-        <v>-0.01815602836879433</v>
-      </c>
-      <c r="J6">
-        <v>-0.0174878865248227</v>
-      </c>
-      <c r="K6">
-        <v>4.82</v>
-      </c>
-      <c r="L6">
-        <v>0.3418439716312057</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0.03360415921485008</v>
-      </c>
-      <c r="AB6">
-        <v>0.03360415921485008</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/nigeria/nigeria_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1833</v>
+        <v>0.166</v>
       </c>
       <c r="E2">
-        <v>0.28135</v>
+        <v>0.196</v>
+      </c>
+      <c r="F2">
+        <v>0.155</v>
       </c>
       <c r="G2">
-        <v>0.003490098532616031</v>
+        <v>0.01973069407866791</v>
       </c>
       <c r="H2">
-        <v>0.003490098532616031</v>
+        <v>0.01973069407866791</v>
       </c>
       <c r="I2">
-        <v>0.00196679585815931</v>
+        <v>0.01424263019284683</v>
       </c>
       <c r="J2">
-        <v>0.001483997411795781</v>
+        <v>0.009842448716057833</v>
       </c>
       <c r="K2">
-        <v>164.51</v>
+        <v>174.583</v>
       </c>
       <c r="L2">
-        <v>0.317213320221361</v>
+        <v>0.3707905020813864</v>
       </c>
       <c r="M2">
-        <v>106.31</v>
+        <v>59.393</v>
       </c>
       <c r="N2">
-        <v>0.09707789242991509</v>
+        <v>0.05088284429213964</v>
       </c>
       <c r="O2">
-        <v>0.646222114157194</v>
+        <v>0.3401992175641386</v>
       </c>
       <c r="P2">
-        <v>106.31</v>
+        <v>59.393</v>
       </c>
       <c r="Q2">
-        <v>0.09707789242991509</v>
+        <v>0.05088284429213964</v>
       </c>
       <c r="R2">
-        <v>0.646222114157194</v>
+        <v>0.3401992175641386</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>420.09</v>
+        <v>827.675</v>
       </c>
       <c r="V2">
-        <v>0.383608802849055</v>
+        <v>0.7090811736988648</v>
       </c>
       <c r="W2">
-        <v>0.1872454323286396</v>
+        <v>0.05490382832386508</v>
       </c>
       <c r="X2">
-        <v>0.07250316683028661</v>
+        <v>0.08584363758626878</v>
       </c>
       <c r="Y2">
-        <v>0.114742265498353</v>
+        <v>-0.03093980926240371</v>
       </c>
       <c r="Z2">
-        <v>0.6949044893233857</v>
+        <v>0.3951869844456605</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.01546144583603566</v>
       </c>
       <c r="AB2">
-        <v>0.07883561814867397</v>
+        <v>0.08797396966059037</v>
       </c>
       <c r="AC2">
-        <v>-0.07883561814867397</v>
+        <v>-0.0764390987823583</v>
       </c>
       <c r="AD2">
-        <v>637.1</v>
+        <v>960.0749999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>637.1</v>
+        <v>960.0749999999999</v>
       </c>
       <c r="AG2">
-        <v>217.01</v>
+        <v>132.4</v>
       </c>
       <c r="AH2">
-        <v>0.3677981757302852</v>
+        <v>0.4513062179027652</v>
       </c>
       <c r="AI2">
-        <v>0.3948387736509726</v>
+        <v>0.586777273691268</v>
       </c>
       <c r="AJ2">
-        <v>0.1653900968668786</v>
+        <v>0.1018735813488247</v>
       </c>
       <c r="AK2">
-        <v>0.1818296075342695</v>
+        <v>0.1637584291064529</v>
       </c>
       <c r="AL2">
-        <v>3.91</v>
+        <v>3.483</v>
       </c>
       <c r="AM2">
-        <v>3.91</v>
+        <v>3.298</v>
       </c>
       <c r="AN2">
-        <v>328.4020618556701</v>
+        <v>112.1059084539935</v>
       </c>
       <c r="AO2">
-        <v>0.2608695652173913</v>
+        <v>1.925351708297445</v>
       </c>
       <c r="AP2">
-        <v>111.860824742268</v>
+        <v>15.46006539000467</v>
       </c>
       <c r="AQ2">
-        <v>0.2608695652173913</v>
+        <v>2.033353547604609</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Nigerian Exchange Group Plc (NGSE:NGXGROUP)</t>
+          <t>eTranzact International Plc (NGSE:ETRANZACT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,23 +724,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.151</v>
+      </c>
       <c r="G3">
-        <v>0.1071005917159763</v>
+        <v>0.1070388349514563</v>
       </c>
       <c r="H3">
-        <v>0.1071005917159763</v>
+        <v>0.1070388349514563</v>
       </c>
       <c r="I3">
-        <v>0.06035502958579882</v>
+        <v>0.07985436893203883</v>
       </c>
       <c r="J3">
-        <v>0.04830697234908993</v>
+        <v>0.05809523467570517</v>
       </c>
       <c r="K3">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="L3">
-        <v>0.1248520710059172</v>
+        <v>0.05970873786407767</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,73 +767,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.2204472843450479</v>
       </c>
       <c r="W3">
-        <v>0.026375</v>
+        <v>0.1194174757281553</v>
       </c>
       <c r="X3">
-        <v>0.07165073593751631</v>
+        <v>0.07622122319935491</v>
       </c>
       <c r="Y3">
-        <v>-0.04527573593751631</v>
-      </c>
-      <c r="Z3">
-        <v>0.256940432389698</v>
-      </c>
-      <c r="AA3">
-        <v>0.01241201436281235</v>
+        <v>0.04319625252880042</v>
       </c>
       <c r="AB3">
-        <v>0.07693872039749275</v>
-      </c>
-      <c r="AC3">
-        <v>-0.0645267060346804</v>
+        <v>0.0763184530479845</v>
       </c>
       <c r="AD3">
-        <v>33.7</v>
+        <v>0.332</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>33.7</v>
+        <v>0.332</v>
       </c>
       <c r="AG3">
-        <v>33.7</v>
+        <v>-13.468</v>
       </c>
       <c r="AH3">
-        <v>0.2348432055749129</v>
+        <v>0.005275535498633446</v>
       </c>
       <c r="AI3">
-        <v>0.2728744939271255</v>
+        <v>0.02332771219786397</v>
       </c>
       <c r="AJ3">
-        <v>0.2348432055749129</v>
+        <v>-0.2741187006431653</v>
       </c>
       <c r="AK3">
-        <v>0.2728744939271255</v>
+        <v>-31.1759259259259</v>
       </c>
       <c r="AL3">
-        <v>3.91</v>
+        <v>0.038</v>
       </c>
       <c r="AM3">
-        <v>3.91</v>
+        <v>-0.147</v>
       </c>
       <c r="AN3">
-        <v>17.37113402061856</v>
+        <v>0.08623376623376623</v>
       </c>
       <c r="AO3">
-        <v>0.2608695652173913</v>
+        <v>86.57894736842105</v>
       </c>
       <c r="AP3">
-        <v>17.37113402061856</v>
+        <v>-3.498181818181818</v>
       </c>
       <c r="AQ3">
-        <v>0.2608695652173913</v>
+        <v>-22.38095238095238</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Livingtrust Mortgage Bank PLC (NGSE:LTBNG)</t>
+          <t>Academy Press Plc (NGSE:ACADEMY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,46 +844,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.27</v>
-      </c>
-      <c r="E4">
-        <v>0.464</v>
+        <v>0.182</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2098360655737705</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.2098360655737705</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.0498360655737705</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.02491803278688525</v>
       </c>
       <c r="K4">
-        <v>1.5</v>
+        <v>-0.244</v>
       </c>
       <c r="L4">
-        <v>0.3480278422273782</v>
+        <v>-0.04</v>
       </c>
       <c r="M4">
-        <v>0.8100000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="N4">
-        <v>0.0452513966480447</v>
+        <v>0.1054545454545455</v>
       </c>
       <c r="O4">
-        <v>0.54</v>
+        <v>-0.7131147540983607</v>
       </c>
       <c r="P4">
-        <v>0.8100000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="Q4">
-        <v>0.0452513966480447</v>
+        <v>0.1054545454545455</v>
       </c>
       <c r="R4">
-        <v>0.54</v>
+        <v>-0.7131147540983607</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,61 +889,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3.29</v>
+        <v>0.04</v>
       </c>
       <c r="V4">
-        <v>0.1837988826815643</v>
+        <v>0.02424242424242425</v>
       </c>
       <c r="W4">
-        <v>0.2252252252252252</v>
+        <v>-0.2346153846153846</v>
       </c>
       <c r="X4">
-        <v>0.07250316683028661</v>
+        <v>0.08704395904867274</v>
       </c>
       <c r="Y4">
-        <v>0.1527220583949386</v>
+        <v>-0.3216593436640574</v>
       </c>
       <c r="Z4">
-        <v>0.6600306278713629</v>
+        <v>1.96837689577283</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.04904808002581477</v>
       </c>
       <c r="AB4">
-        <v>0.07883561814867397</v>
+        <v>0.08929409188303837</v>
       </c>
       <c r="AC4">
-        <v>-0.07883561814867397</v>
+        <v>-0.0402460118572236</v>
       </c>
       <c r="AD4">
-        <v>6.3</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6.3</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AG4">
-        <v>3.01</v>
+        <v>0.6529999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.2603305785123967</v>
+        <v>0.2957746478873239</v>
       </c>
       <c r="AI4">
-        <v>0.4820198928844682</v>
+        <v>0.5770191507077435</v>
       </c>
       <c r="AJ4">
-        <v>0.1439502630320421</v>
+        <v>0.2835432045158489</v>
       </c>
       <c r="AK4">
-        <v>0.3077709611451943</v>
+        <v>0.5624461670973298</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="AN4">
+        <v>1.184615384615385</v>
+      </c>
+      <c r="AO4">
+        <v>1.351111111111111</v>
+      </c>
+      <c r="AP4">
+        <v>1.116239316239316</v>
+      </c>
+      <c r="AQ4">
+        <v>1.351111111111111</v>
       </c>
     </row>
     <row r="5">
@@ -960,118 +966,499 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>The Nigerian Exchange Group Plc (NGSE:NGXGROUP)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0.1859375</v>
+      </c>
+      <c r="H5">
+        <v>0.1859375</v>
+      </c>
+      <c r="I5">
+        <v>0.22890625</v>
+      </c>
+      <c r="J5">
+        <v>0.1755734536082474</v>
+      </c>
+      <c r="K5">
+        <v>2.24</v>
+      </c>
+      <c r="L5">
+        <v>0.175</v>
+      </c>
+      <c r="M5">
+        <v>0.635</v>
+      </c>
+      <c r="N5">
+        <v>0.01089193825042882</v>
+      </c>
+      <c r="O5">
+        <v>0.2834821428571428</v>
+      </c>
+      <c r="P5">
+        <v>0.635</v>
+      </c>
+      <c r="Q5">
+        <v>0.01089193825042882</v>
+      </c>
+      <c r="R5">
+        <v>0.2834821428571428</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>6.65</v>
+      </c>
+      <c r="V5">
+        <v>0.114065180102916</v>
+      </c>
+      <c r="W5">
+        <v>0.02586605080831409</v>
+      </c>
+      <c r="X5">
+        <v>0.08414050408868079</v>
+      </c>
+      <c r="Y5">
+        <v>-0.0582744532803667</v>
+      </c>
+      <c r="Z5">
+        <v>0.113656544130705</v>
+      </c>
+      <c r="AA5">
+        <v>0.01995507197820606</v>
+      </c>
+      <c r="AB5">
+        <v>0.08617942210478029</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06622435012657422</v>
+      </c>
+      <c r="AD5">
+        <v>18</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>18</v>
+      </c>
+      <c r="AG5">
+        <v>11.35</v>
+      </c>
+      <c r="AH5">
+        <v>0.235910878112713</v>
+      </c>
+      <c r="AI5">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AJ5">
+        <v>0.1629576453697057</v>
+      </c>
+      <c r="AK5">
+        <v>0.1912384161752317</v>
+      </c>
+      <c r="AL5">
+        <v>3.09</v>
+      </c>
+      <c r="AM5">
+        <v>3.09</v>
+      </c>
+      <c r="AN5">
+        <v>5.309734513274336</v>
+      </c>
+      <c r="AO5">
+        <v>0.9482200647249192</v>
+      </c>
+      <c r="AP5">
+        <v>3.348082595870206</v>
+      </c>
+      <c r="AQ5">
+        <v>0.9482200647249192</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Infinity Trust Mortgage Bank Plc (NGSE:INFINITY)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.181</v>
+      </c>
+      <c r="E6">
+        <v>0.251</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1.15</v>
+      </c>
+      <c r="L6">
+        <v>0.4423076923076922</v>
+      </c>
+      <c r="M6">
+        <v>0.321</v>
+      </c>
+      <c r="N6">
+        <v>0.01138297872340426</v>
+      </c>
+      <c r="O6">
+        <v>0.2791304347826087</v>
+      </c>
+      <c r="P6">
+        <v>0.321</v>
+      </c>
+      <c r="Q6">
+        <v>0.01138297872340426</v>
+      </c>
+      <c r="R6">
+        <v>0.2791304347826087</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1.68</v>
+      </c>
+      <c r="V6">
+        <v>0.05957446808510639</v>
+      </c>
+      <c r="W6">
+        <v>0.08394160583941605</v>
+      </c>
+      <c r="X6">
+        <v>0.08464331612386485</v>
+      </c>
+      <c r="Y6">
+        <v>-0.0007017102844487921</v>
+      </c>
+      <c r="Z6">
+        <v>0.1073492981007432</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.08665384743814239</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08665384743814239</v>
+      </c>
+      <c r="AD6">
+        <v>9.25</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>9.25</v>
+      </c>
+      <c r="AG6">
+        <v>7.57</v>
+      </c>
+      <c r="AH6">
+        <v>0.2469959946595461</v>
+      </c>
+      <c r="AI6">
+        <v>0.512749445676275</v>
+      </c>
+      <c r="AJ6">
+        <v>0.211629857422421</v>
+      </c>
+      <c r="AK6">
+        <v>0.4627139364303179</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Stanbic IBTC Holdings PLC (NGSE:STANBIC)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.09660000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.0987</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>160.9</v>
-      </c>
-      <c r="L5">
-        <v>0.3234821069561721</v>
-      </c>
-      <c r="M5">
-        <v>105.5</v>
-      </c>
-      <c r="N5">
-        <v>0.1090551995038247</v>
-      </c>
-      <c r="O5">
-        <v>0.6556867619639527</v>
-      </c>
-      <c r="P5">
-        <v>105.5</v>
-      </c>
-      <c r="Q5">
-        <v>0.1090551995038247</v>
-      </c>
-      <c r="R5">
-        <v>0.6556867619639527</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>416.8</v>
-      </c>
-      <c r="V5">
-        <v>0.4308455654331197</v>
-      </c>
-      <c r="W5">
-        <v>0.1872454323286396</v>
-      </c>
-      <c r="X5">
-        <v>0.0775243259134827</v>
-      </c>
-      <c r="Y5">
-        <v>0.1097211064151569</v>
-      </c>
-      <c r="Z5">
-        <v>0.7379821958456972</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.08489161065392201</v>
-      </c>
-      <c r="AC5">
-        <v>-0.08489161065392201</v>
-      </c>
-      <c r="AD5">
-        <v>597.1</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>597.1</v>
-      </c>
-      <c r="AG5">
-        <v>180.3</v>
-      </c>
-      <c r="AH5">
-        <v>0.38165548098434</v>
-      </c>
-      <c r="AI5">
-        <v>0.4042654028436019</v>
-      </c>
-      <c r="AJ5">
-        <v>0.1570968023002527</v>
-      </c>
-      <c r="AK5">
-        <v>0.1700622524052066</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
+      <c r="D7">
+        <v>0.115</v>
+      </c>
+      <c r="E7">
+        <v>0.141</v>
+      </c>
+      <c r="F7">
+        <v>0.155</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>169</v>
+      </c>
+      <c r="L7">
+        <v>0.4177997527812114</v>
+      </c>
+      <c r="M7">
+        <v>58.2</v>
+      </c>
+      <c r="N7">
+        <v>0.05732295873140944</v>
+      </c>
+      <c r="O7">
+        <v>0.3443786982248521</v>
+      </c>
+      <c r="P7">
+        <v>58.2</v>
+      </c>
+      <c r="Q7">
+        <v>0.05732295873140944</v>
+      </c>
+      <c r="R7">
+        <v>0.3443786982248521</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>805.5</v>
+      </c>
+      <c r="V7">
+        <v>0.7933615680094553</v>
+      </c>
+      <c r="W7">
+        <v>0.1958511994437362</v>
+      </c>
+      <c r="X7">
+        <v>0.09993162072064678</v>
+      </c>
+      <c r="Y7">
+        <v>0.09591957872308947</v>
+      </c>
+      <c r="Z7">
+        <v>0.3877492331288344</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.0965183854701518</v>
+      </c>
+      <c r="AC7">
+        <v>-0.0965183854701518</v>
+      </c>
+      <c r="AD7">
+        <v>927.8</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>927.8</v>
+      </c>
+      <c r="AG7">
+        <v>122.3</v>
+      </c>
+      <c r="AH7">
+        <v>0.4774844320930472</v>
+      </c>
+      <c r="AI7">
+        <v>0.6058904199046562</v>
+      </c>
+      <c r="AJ7">
+        <v>0.1075070323488045</v>
+      </c>
+      <c r="AK7">
+        <v>0.1685037200330669</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tripple Gee &amp; Company Plc (NGSE:TRIPPLEG)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0.3351648351648351</v>
+      </c>
+      <c r="H8">
+        <v>0.3351648351648351</v>
+      </c>
+      <c r="I8">
+        <v>0.05</v>
+      </c>
+      <c r="J8">
+        <v>0.025</v>
+      </c>
+      <c r="K8">
+        <v>-0.023</v>
+      </c>
+      <c r="L8">
+        <v>-0.006318681318681319</v>
+      </c>
+      <c r="M8">
+        <v>0.063</v>
+      </c>
+      <c r="N8">
+        <v>0.0525</v>
+      </c>
+      <c r="O8">
+        <v>-2.739130434782609</v>
+      </c>
+      <c r="P8">
+        <v>0.063</v>
+      </c>
+      <c r="Q8">
+        <v>0.0525</v>
+      </c>
+      <c r="R8">
+        <v>-2.739130434782609</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0.005</v>
+      </c>
+      <c r="V8">
+        <v>0.004166666666666667</v>
+      </c>
+      <c r="W8">
+        <v>-0.01329479768786127</v>
+      </c>
+      <c r="X8">
+        <v>0.1630760408260503</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1763708385139116</v>
+      </c>
+      <c r="Z8">
+        <v>0.4387127877546101</v>
+      </c>
+      <c r="AA8">
+        <v>0.01096781969386525</v>
+      </c>
+      <c r="AB8">
+        <v>0.110441817892535</v>
+      </c>
+      <c r="AC8">
+        <v>-0.09947399819866971</v>
+      </c>
+      <c r="AD8">
+        <v>4</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>4</v>
+      </c>
+      <c r="AG8">
+        <v>3.995</v>
+      </c>
+      <c r="AH8">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="AI8">
+        <v>0.7393715341959335</v>
+      </c>
+      <c r="AJ8">
+        <v>0.7690086621751684</v>
+      </c>
+      <c r="AK8">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="AL8">
+        <v>0.13</v>
+      </c>
+      <c r="AM8">
+        <v>0.13</v>
+      </c>
+      <c r="AN8">
+        <v>5.412719891745602</v>
+      </c>
+      <c r="AO8">
+        <v>1.4</v>
+      </c>
+      <c r="AP8">
+        <v>5.405953991880921</v>
+      </c>
+      <c r="AQ8">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
